--- a/Econ/Data/econ04.2.xlsx
+++ b/Econ/Data/econ04.2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A39AAFA3-7337-4535-96EE-96029FF4D8D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E9D3815-C2AC-484D-B168-FCE1DD759D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11949" xr2:uid="{F705FF06-4732-4CDD-94EF-6491BB3D6C63}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>Population (thousands)</t>
   </si>
@@ -60,13 +60,28 @@
     <t>פירסום</t>
   </si>
   <si>
-    <t>שנה</t>
+    <t>חודש</t>
+  </si>
+  <si>
+    <t>קיץ</t>
+  </si>
+  <si>
+    <t>חורף</t>
+  </si>
+  <si>
+    <t>אביב</t>
+  </si>
+  <si>
+    <t>סתיו</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -96,9 +111,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -433,10 +449,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{596C3521-318D-40C8-A428-21E2F3A06039}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultRowHeight="12.45" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -449,8 +465,23 @@
       <c r="D1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -463,8 +494,23 @@
       <c r="D2" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -477,8 +523,23 @@
       <c r="D3" s="1">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2">
+        <v>1</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -491,8 +552,23 @@
       <c r="D4" s="1">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -505,8 +581,23 @@
       <c r="D5" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -519,8 +610,23 @@
       <c r="D6" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -533,8 +639,23 @@
       <c r="D7" s="1">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -547,8 +668,23 @@
       <c r="D8" s="1">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E8" s="2">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -561,8 +697,23 @@
       <c r="D9" s="1">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -575,8 +726,23 @@
       <c r="D10" s="1">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E10" s="2">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -589,8 +755,23 @@
       <c r="D11" s="1">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E11" s="2">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -603,8 +784,23 @@
       <c r="D12" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -617,8 +813,23 @@
       <c r="D13" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -631,8 +842,23 @@
       <c r="D14" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -645,8 +871,23 @@
       <c r="D15" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2">
+        <v>1</v>
+      </c>
+      <c r="H15" s="2">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -658,6 +899,21 @@
       </c>
       <c r="D16" s="1">
         <v>4.5</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2">
+        <v>1</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
